--- a/Rania/500-1/500-1-MDM-HES.xlsx
+++ b/Rania/500-1/500-1-MDM-HES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Downloads\Rania\500-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A436C18C-607A-4F29-872C-C3C11B87B449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B2461F-33DA-4B38-ABF3-758B7CD0E195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" tabRatio="902" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="450" windowWidth="12000" windowHeight="13050" tabRatio="601" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HES" sheetId="4" r:id="rId1"/>
